--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104924</v>
+        <v>104931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104931</v>
+        <v>104934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104934</v>
+        <v>104938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104938</v>
+        <v>104939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104939</v>
+        <v>104941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104941</v>
+        <v>104943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104943</v>
+        <v>104947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104947</v>
+        <v>104960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6000-2023 artfynd.xlsx
+++ b/artfynd/A 6000-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125782249</v>
       </c>
       <c r="B2" t="n">
-        <v>104960</v>
+        <v>104963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
